--- a/plantilla_tarifas_telefonia_importacion.xlsx
+++ b/plantilla_tarifas_telefonia_importacion.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="85">
   <si>
     <t>ID</t>
   </si>
@@ -125,6 +125,24 @@
     <t>6 meses</t>
   </si>
   <si>
+    <t>Pepephone</t>
+  </si>
+  <si>
+    <t>MovilAdicional</t>
+  </si>
+  <si>
+    <t>Línea adicional 30GB</t>
+  </si>
+  <si>
+    <t>30 GB</t>
+  </si>
+  <si>
+    <t>10,00</t>
+  </si>
+  <si>
+    <t>15,00</t>
+  </si>
+  <si>
     <t>Jazztel</t>
   </si>
   <si>
@@ -185,6 +203,9 @@
     <t xml:space="preserve">    * Movil (Solo Móvil)</t>
   </si>
   <si>
+    <t xml:space="preserve">    * MovilAdicional (Líneas móviles adicionales para FibraMovil, Movil y FibraMovilTV)</t>
+  </si>
+  <si>
     <t xml:space="preserve">    * FibraMovilTV (Fibra, Móvil y TV)</t>
   </si>
   <si>
@@ -248,7 +269,7 @@
     <t>- Las filas completamente vacías se ignorarán</t>
   </si>
   <si>
-    <t>- Se proporcionan 5 ejemplos, uno de cada tipo válido de tarifa</t>
+    <t>- Se proporcionan 6 ejemplos, uno de cada tipo válido de tarifa</t>
   </si>
 </sst>
 </file>
@@ -635,7 +656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="13" width="18.7109375" customWidth="1"/>
@@ -788,25 +809,21 @@
       <c r="D5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
         <v>39</v>
       </c>
       <c r="G5" s="2"/>
-      <c r="H5" s="2" t="s">
-        <v>40</v>
-      </c>
+      <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="L5" s="2" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>21</v>
@@ -815,31 +832,66 @@
     <row r="6" spans="1:13">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="E6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="G6" s="2"/>
+      <c r="H6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>48</v>
       </c>
       <c r="L6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="L7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -850,7 +902,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="80.7109375" customWidth="1"/>
@@ -858,147 +910,152 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="4" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="4" t="s">
-        <v>60</v>
+      <c r="A13" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>61</v>
+      <c r="A16" s="4" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="4" t="s">
-        <v>71</v>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>72</v>
+      <c r="A28" s="4" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>77</v>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
